--- a/doc/HyperParameters.xlsx
+++ b/doc/HyperParameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\papyrus\uni\papyrus_master\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E658ED0-B714-441E-ADBA-3C4C09287C30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF5703F6-C8EB-41CA-85DF-7EDCDB8724E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2F31703B-80AB-4B33-A473-064842AE7FDA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2F31703B-80AB-4B33-A473-064842AE7FDA}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="28">
   <si>
     <t>Data_augmentation</t>
   </si>
@@ -53,9 +53,6 @@
     <t>No / Yes / Mixed</t>
   </si>
   <si>
-    <t>N°</t>
-  </si>
-  <si>
     <t>Fixed</t>
   </si>
   <si>
@@ -107,16 +104,22 @@
     <t>positional_learnable</t>
   </si>
   <si>
-    <t xml:space="preserve">0, 1, 10 </t>
-  </si>
-  <si>
-    <t>0, 1, 10</t>
-  </si>
-  <si>
     <t>4, 8, 16</t>
   </si>
   <si>
-    <t>4, 10</t>
+    <t>Structural</t>
+  </si>
+  <si>
+    <t>HyperParam</t>
+  </si>
+  <si>
+    <t>[0-1]</t>
+  </si>
+  <si>
+    <t>LR=1e-4; W=1; HEADS=8; LAYERS=6</t>
+  </si>
+  <si>
+    <t>6, 12</t>
   </si>
 </sst>
 </file>
@@ -490,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F9F8C62-6E21-463D-9AE6-28D4294C4921}">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="48" customWidth="1"/>
@@ -503,10 +506,10 @@
         <v>1</v>
       </c>
       <c r="J1" t="s">
+        <v>5</v>
+      </c>
+      <c r="K1" t="s">
         <v>6</v>
-      </c>
-      <c r="K1" t="s">
-        <v>7</v>
       </c>
       <c r="L1">
         <v>16</v>
@@ -519,11 +522,8 @@
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
       <c r="K2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L2">
         <v>256</v>
@@ -531,94 +531,113 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="K3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L3">
         <v>96.96</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
       <c r="K4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L4" t="s">
         <v>10</v>
       </c>
-      <c r="L4" t="s">
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K5" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="K5" t="s">
-        <v>12</v>
       </c>
       <c r="L5">
         <v>500</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-    </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="B9" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
+      </c>
+      <c r="B10" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>19</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>20</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>21</v>
-      </c>
-      <c r="B14" t="s">
-        <v>26</v>
+      <c r="B23" t="s">
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/doc/HyperParameters.xlsx
+++ b/doc/HyperParameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\papyrus\uni\papyrus_master\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF5703F6-C8EB-41CA-85DF-7EDCDB8724E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{863EFC91-642C-4612-8082-6CD9419AE27F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2F31703B-80AB-4B33-A473-064842AE7FDA}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2F31703B-80AB-4B33-A473-064842AE7FDA}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
